--- a/data/bangla_pragmatics_responses.xlsx
+++ b/data/bangla_pragmatics_responses.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Responses" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Usability_Feedback" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,3063 +413,3541 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="15.88671875" customWidth="1" min="6" max="6"/>
+    <col width="20.44140625" customWidth="1" min="7" max="7"/>
+    <col width="16.21875" customWidth="1" min="9" max="9"/>
+    <col width="111.21875" customWidth="1" min="10" max="10"/>
+    <col width="32.88671875" customWidth="1" min="11" max="11"/>
+    <col width="20.44140625" customWidth="1" min="12" max="12"/>
+    <col width="15.88671875" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Response_ID</t>
+          <t>f1b3b0cf-7f0c-4980-a233-b7f14ea66390</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Participant_Age_Group</t>
+          <t>2026-09-01T22:11:10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Bangla_Usage</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Bangla_Variety</t>
+          <t>Almost always</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Scenario_ID</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Scenario_Category</t>
-        </is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H1" t="n">
+        <v>1</v>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Context</t>
+          <t>Direct Request</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Utterance</t>
+          <t>আপনি আপনার ঘরে পড়াশোনা করছেন। পাশের ঘরে আপনার ছোট ভাই/বোন খুব জোরে গান বাজাচ্ছে এবং আপনি মনোযোগ দিতে পারছেন না।</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Intended_Meaning</t>
-        </is>
+          <t>বোন, গানটা একটু আস্তে বাজাও তো।</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>বোনকে সরাসরি বলছি যেন গানটা আস্তে বাজায়।</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>অনুরোধ (Request)</t>
+        </is>
+      </c>
+      <c r="N1" t="n">
+        <v>17.82</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6e315b6b-9c07-4817-8f73-3ddd8b109aa5</t>
+          <t>fda07b14-1911-4c60-8eae-61ef3065ba80</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19T00:15:11</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:13:55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Direct Request</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>আপনি আপনার ঘরে পড়াশোনা করছেন। পাশের ঘরে আপনার ছোট ভাই/বোন খুব জোরে গান বাজাচ্ছে এবং আপনি মনোযোগ দিতে পারছেন না।</t>
+          <t>Indirect Request</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ভাই, একটু আস্তে বাজাও।</t>
+          <t>আপনি একজন বন্ধুর সঙ্গে একটি ঘরে বসে আছেন। জানালা খোলা এবং বাইরে অনেক ঠান্ডা।</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>আমি পড়াশোনায় মনোযোগ দিতে চাই।</t>
+          <t>আজকে আবহাওয়াটা বেশ ঠান্ডা, না?</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>বন্ধুকে পরোক্ষভাবে জানালাটা বন্ধ করতে বলা।</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>অনুরোধ (Request)</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>148.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8d01390f-9de4-42ce-ad81-92314bfd3105</t>
+          <t>10df913f-5cd8-4e55-b204-0d803b93811a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19T00:15:43</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:14:14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Indirect Request</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>আপনি একজন বন্ধুর সঙ্গে একটি ঘরে বসে আছেন। জানালা খোলা এবং বাইরে অনেক ঠান্ডা।</t>
+          <t>Asking Someone to Move</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>আজকে আবহাওয়াটা একটু বেশিই ঠান্ডা, না?</t>
+          <t>আপনি বাসে বসতে যাচ্ছেন। পাশের আসনে একজন তার ব্যাগ রেখেছে এবং আপনি সেখানে বসতে চান।</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>রোক্ষভাবে বন্ধুকে জানালাটা বন্ধ করতে বলা।</t>
+          <t>ভাই, ব্যাগটা সরিয়ে দেবেন? আমি বসতে চাই।</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>ভদ্রভাবে আসন খালি করতে বলা।</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>অনুরোধ (Request)</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>18.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>db4b05ff-25e4-47e6-9014-36f45350cf85</t>
+          <t>9d301136-09ae-40d4-ad7e-2f36412fa8b3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T00:16:55</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:14:35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Asking Someone to Move</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>আপনি বাসে বসতে যাচ্ছেন। পাশের আসনে একজন তার ব্যাগ রেখেছে এবং আপনি সেখানে বসতে চান।</t>
+          <t>Request for Help</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>আমি এখানে বসতে চাই, ব্যাগটা কি সরাবেন?</t>
+          <t>আপনার হাতে কয়েকটি ভারী ব্যাগ এবং আপনার বন্ধু কাছেই দাঁড়িয়ে আছে।</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>আমি বসতে চাই, তাই ব্যাগ সরাতে বলছি।</t>
+          <t>এই ব্যাগগুলো একটু ধরো তো।</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>বন্ধুকে সাহায্য করতে বলা।</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>অনুরোধ (Request)</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>21.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>c5dc1435-b104-466e-a957-187718bbc9b1</t>
+          <t>77770d3c-eddc-4b0a-8a1b-094c51965e82</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19T00:18:21</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:14:54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Request for Help</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>আপনার হাতে কয়েকটি ভারী ব্যাগ এবং আপনার বন্ধু কাছেই দাঁড়িয়ে আছে।</t>
+          <t>Indirect Request to Stop</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>এই ব্যাগগুলো ধরতে একটু সাহায্য করো।</t>
+          <t>গুরুত্বপূর্ণ পরীক্ষার প্রস্তুতির সময় আপনার বন্ধু বারবার আপনাকে মেসেজ পাঠাচ্ছে।</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ভারী জিনিস বহনে সাহায্য চাই।</t>
+          <t>আমি পড়াশোনা করছি, পরে কথা বলি।</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>বন্ধুকে পরোক্ষভাবে মেসেজ পাঠানো বন্ধ করতে বলা।</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>অনুরোধ (Request)</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>18.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6cea4e51-47b9-4683-aebe-07a76b3dbfd9</t>
+          <t>532afef6-c50f-4029-8fc2-272e4cdbb6dc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-19T00:18:54</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:15:38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Indirect Request to Stop</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>গুরুত্বপূর্ণ পরীক্ষার প্রস্তুতির সময় আপনার বন্ধু বারবার আপনাকে মেসেজ পাঠাচ্ছে।</t>
+          <t>Direct Refusal</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>আমি পড়াশোনায় ব্যস্ত আছি।</t>
+          <t>আপনার বন্ধু আপনাকে একটি পার্টিতে যেতে বলেছে, কিন্তু পরদিন সকালে আপনার গুরুত্বপূর্ণ পরীক্ষা।</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>আমি পড়াশোনায় ব্যস্ত আছি।</t>
+          <t>না, আমি পার্টিতে যেতে পারব না। কাল পরীক্ষা আছে।</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>পরীক্ষার কারণে পার্টিতে না যাওয়া।</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>44.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c222f1b6-a620-49bb-af98-882ff3583fa1</t>
+          <t>cc3c541a-e09f-45e2-984d-41e40d943377</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-19T00:19:27</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:15:57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Direct Refusal</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু আপনাকে একটি পার্টিতে যেতে বলেছে, কিন্তু পরদিন সকালে আপনার গুরুত্বপূর্ণ পরীক্ষা।</t>
+          <t>Indirect Refusal</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>না, আমি পার্টিতে যেতে পারব না।</t>
+          <t>একজন বন্ধু জিজ্ঞেস করল: “কাল আমার সাথে ঘুরতে যাবে?” কিন্তু আপনার আগে থেকেই অন্য একটি কাজ আছে।</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>পরীক্ষার কারণে অস্বীকৃতি।</t>
+          <t>কাল আমার অন্য কাজ আছে।</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>ঘুরতে যাওয়ার প্রস্তাব প্রত্যাখ্যান।</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>19.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>602db9c8-e813-4905-ab84-697fd313587e</t>
+          <t>1f866eca-454d-497d-8727-d5b17c8a587e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19T00:20:08</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:16:18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Indirect Refusal</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>একজন বন্ধু জিজ্ঞেস করল: “কাল আমার সাথে ঘুরতে যাবে?” কিন্তু আপনার আগে থেকেই অন্য একটি কাজ আছে।</t>
+          <t>Polite Refusal</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>আগে থেকেই অন্য কাজ আছে।</t>
+          <t>একজন সহকর্মী আপনাকে আজ অতিরিক্ত কাজ করতে বলেছে, কিন্তু আপনি ইতিমধ্যে অনেক কাজের চাপে আছেন।</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ঘুরতে যাওয়ার প্রস্তাব প্রত্যাখ্যান।</t>
+          <t>আজকে সম্ভব হবে না, অনেক কাজ জমে আছে।</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>অতিরিক্ত কাজ politely না বলা।</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>20.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3628a5e6-1c6f-4fcd-809d-b41e389f5d21</t>
+          <t>ee561601-00c0-4e4c-825c-227bcb56601a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-19T00:20:38</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:16:37</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Polite Refusal</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>একজন সহকর্মী আপনাকে আজ অতিরিক্ত কাজ করতে বলেছে, কিন্তু আপনি ইতিমধ্যে অনেক কাজের চাপে আছেন।</t>
+          <t>Avoiding an Invitation</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>দুঃখিত, আজ আর কাজ নিতে পারব না।</t>
+          <t>আপনাকে এমন একজন ব্যক্তি ডিনারে আমন্ত্রণ জানিয়েছে যাকে আপনি খুব বেশি চেনেন না, কিন্তু আপনি যেতে চান না।</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>অতিরিক্ত কাজ না করার ভদ্র অস্বীকৃতি।</t>
+          <t>আসলে আমি ব্যস্ত আছি, অন্যদিন দেখা হবে।</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>আসলে আমি ব্যস্ত আছি, অন্যদিন দেখা হবে।</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N9" t="n">
+        <v>19.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e08af75e-a8d7-48e9-8ebe-dfe2034e7e21</t>
+          <t>9e847295-2160-4ce4-b677-01c64159a81d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-19T00:21:17</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:16:54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Avoiding an Invitation</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>আপনাকে এমন একজন ব্যক্তি ডিনারে আমন্ত্রণ জানিয়েছে যাকে আপনি খুব বেশি চেনেন না, কিন্তু আপনি যেতে চান না।</t>
+          <t>Refusing to Lend</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>আজ আমার অন্য পরিকল্পনা আছে।</t>
+          <t>একজন বন্ধু আপনার ল্যাপটপ ধার চাইছে, কিন্তু আপনি ল্যাপটপটি দিতে চান না।</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ডিনারে না যাওয়ার অজুহাত।</t>
+          <t>দুঃখিত, ল্যাপটপটা এখন দরকার।</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>ল্যাপটপ ধার না দেওয়া।</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>16.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1bae88a1-d6c9-4c16-99d8-7036aa84c31d</t>
+          <t>948fbb1d-3d94-4cc6-a019-57c5b8efdd2f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-19T00:21:50</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:17:12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Refusing to Lend</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>একজন বন্ধু আপনার ল্যাপটপ ধার চাইছে, কিন্তু আপনি ল্যাপটপটি দিতে চান না।</t>
+          <t>Sarcasm: Late Arrival</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ল্যাপটপটা এখন দরকার, দিতে পারব না।</t>
+          <t>আপনার বন্ধু বিকেল ৫টায় আসার কথা বলেছিল, কিন্তু সে রাত ৭টায় এসে পৌঁছাল।</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ল্যাপটপ ধার না দেওয়া।</t>
+          <t>বাহ, একদম সময়মতো এসেছো!</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>বন্ধুর দেরি নিয়ে ব্যঙ্গ।</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>18.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f8212a5e-5a04-4d12-9cea-332762afb224</t>
+          <t>db1fd573-3467-4df8-9a40-bb3847ad4ae3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19T00:22:39</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:17:28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sarcasm: Late Arrival</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু বিকেল ৫টায় আসার কথা বলেছিল, কিন্তু সে রাত ৭টায় এসে পৌঁছাল।</t>
+          <t>Sarcasm: Poor Performance</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ওহ, তুমি তো একদম সময়মতো এসেছো!</t>
+          <t>আপনার বন্ধু একটি কাজকে খুব সহজ বলেছিল, কিন্তু শেষ পর্যন্ত সে কাজটি সম্পূর্ণ করতে ব্যর্থ হয়েছে।</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>দেরি করার জন্য ব্যঙ্গ।</t>
+          <t>ওহ, কাজটা তো খুব সহজ ছিল!</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>ব্যর্থতায় ঠাট্টা।</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N12" t="n">
+        <v>15.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dd3e404b-14da-4728-a931-ebe7a8a227d6</t>
+          <t>a143c882-c0cd-4093-86c4-0fa43a7a39af</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-19T00:23:07</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:17:50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sarcasm: Poor Performance</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু একটি কাজকে খুব সহজ বলেছিল, কিন্তু শেষ পর্যন্ত সে কাজটি সম্পূর্ণ করতে ব্যর্থ হয়েছে।</t>
+          <t>Sarcasm: Messy Room</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>কাজটা তো খুব সহজ ছিল, তাই না?</t>
+          <t>আপনার ভাই/বোন ঘর পরিষ্কার করবে বলেছিল, কিন্তু ঘরটি আরও বেশি এলোমেলো করে ফেলেছে।</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ব্যর্থতার জন্য ঠাট্টা।</t>
+          <t>ঘরটা তো একদম ঝকঝকে করেছো!</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>এলোমেলো ঘর নিয়ে ব্যঙ্গ।</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N13" t="n">
+        <v>21.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3a770eb6-62c9-48a9-9f80-cd341d75dbf2</t>
+          <t>53d99af2-5843-445b-a607-8168123c6942</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-19T00:23:36</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:18:05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sarcasm: Messy Room</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>আপনার ভাই/বোন ঘর পরিষ্কার করবে বলেছিল, কিন্তু ঘরটি আরও বেশি এলোমেলো করে ফেলেছে।</t>
+          <t>Sarcasm: Broken Promise</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>কি সুন্দরভাবে ঘর পরিষ্কার করেছো</t>
+          <t>আপনার বন্ধু কয়েকবার আপনাকে ফোন করবে বলেছিল, কিন্তু কখনো ফোন করেনি। অবশেষে সে ফোন করল।</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>এলোমেলো করার জন্য ব্যঙ্গ।</t>
+          <t>অবশেষে মনে পড়ল ফোন করার কথা!</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>প্রতিশ্রুতি ভাঙায় ব্যঙ্গ।</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N14" t="n">
+        <v>15.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2bd045f4-0789-4139-ba7c-0f5d02419949</t>
+          <t>b1d9f56a-2512-4067-b14b-71b513dd89fd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-19T00:24:45</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:18:23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sarcasm: Broken Promise</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>15</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু কয়েকবার আপনাকে ফোন করবে বলেছিল, কিন্তু কখনো ফোন করেনি। অবশেষে সে ফোন করল।</t>
+          <t>Sarcasm: Obvious Mistake</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>অবশেষে ফোন করলে, দারুণ!</t>
+          <t>আপনার বন্ধু একটি খুব স্পষ্ট ভুল করেছে এবং বলছে, “আমি কখনো ভুল করি না।”</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>প্রতিশ্রুতি ভঙ্গের জন্য ব্যঙ্গ।</t>
+          <t>হ্যাঁ, তুমি তো কখনো ভুল করো না।</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>স্পষ্ট ভুল নিয়ে ব্যঙ্গ।</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N15" t="n">
+        <v>17.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>abbfab0d-897f-4704-85bd-6e06ff7be8ab</t>
+          <t>9be68f61-8c4a-45de-b131-55251506e486</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-19T00:25:40</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:18:48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>15</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sarcasm: Obvious Mistake</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>16</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু একটি খুব স্পষ্ট ভুল করেছে এবং বলছে, “আমি কখনো ভুল করি না।”</t>
+          <t>Irony: Rain</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>তুমি তো কখনো ভুল করো না!</t>
+          <t>আপনি সারাদিনের জন্য একটি বাইরের অনুষ্ঠান আয়োজন করেছেন, কিন্তু অনুষ্ঠান শুরুর সময় প্রচণ্ড বৃষ্টি শুরু হলো।</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>স্পষ্ট ভুলের জন্য ব্যঙ্গ।</t>
+          <t>কি সুন্দর সময়ে বৃষ্টি হলো!</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>অনুষ্ঠান নষ্ট হওয়ায় বিদ্রূপ।</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N16" t="n">
+        <v>25.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e3420308-18b6-46ab-ac6f-dceae2dbc975</t>
+          <t>816dba8c-2c09-4d9c-b3cd-32a2e9b39918</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-19T00:26:14</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:19:08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Irony: Rain</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>আপনি সারাদিনের জন্য একটি বাইরের অনুষ্ঠান আয়োজন করেছেন, কিন্তু অনুষ্ঠান শুরুর সময় প্রচণ্ড বৃষ্টি শুরু হলো।</t>
+          <t>Irony: Technology Failure</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>কি দারুণ সময় বৃষ্টি শুরু হলো।</t>
+          <t>আপনি নতুন একটি ফোন কিনেছেন কারণ আপনি আশা করেছিলেন এটি খুব ভালো কাজ করবে, কিন্তু প্রথম দিনেই ফোনটি নষ্ট হয়ে গেল।</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>হতাশা প্রকাশ।</t>
+          <t>নতুন ফোনটা দারুণ কাজ করছে, তাই না?</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>ফোন নষ্ট হওয়ায় বিদ্রূপ।</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>19.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8ba5fc04-42b0-47a6-b73a-9a01a2e1196a</t>
+          <t>fb4df79e-80b8-408d-8954-a06c0cf77284</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-19T00:26:49</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:19:23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>17</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Irony: Technology Failure</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>18</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>আপনি নতুন একটি ফোন কিনেছেন কারণ আপনি আশা করেছিলেন এটি খুব ভালো কাজ করবে, কিন্তু প্রথম দিনেই ফোনটি নষ্ট হয়ে গেল।</t>
+          <t>Irony: Perfect Timing</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>নতুন ফোনটা একদম চমৎকার কাজ করছে।</t>
+          <t>আপনি বাসস্ট্যান্ডে পৌঁছানোর ঠিক পরেই আপনার বাসটি ছেড়ে দিল।</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ফোন নষ্ট হওয়ার জন্য ব্যঙ্গ।</t>
+          <t>বাহ, ঠিক আমার আসার সময়েই বাসটা গেল।</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>খারাপ সময় নিয়ে বিদ্রূপ।</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N18" t="n">
+        <v>15.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7fe6db0d-4597-4b8f-b956-d01e17ab2490</t>
+          <t>6800a135-0971-4900-989b-96d5dcf6b4d0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-19T00:27:24</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:19:37</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>18</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Irony: Perfect Timing</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>আপনি বাসস্ট্যান্ডে পৌঁছানোর ঠিক পরেই আপনার বাসটি ছেড়ে দিল।</t>
+          <t>Irony: Group Project</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>বাসটা ঠিক আমার সামনে চলে গেল।</t>
+          <t>আপনার গ্রুপের সদস্যরা প্রায় কোনো কাজ না করে শেষ মুহূর্তে ডেডলাইনের এক মিনিট আগে অ্যাসাইনমেন্ট জমা দিল।</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>দুর্ভাগ্য প্রকাশ।</t>
+          <t>আমাদের টিমওয়ার্ক সত্যিই অসাধারণ!</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>খারাপ গ্রুপ কাজ নিয়ে বিদ্রূপ।</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>14.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcdf813c-8893-49f6-bd49-f529a172301f</t>
+          <t>d37787f8-69d6-45e3-8a0f-99e55b85cd7b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-19T00:28:33</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:19:52</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>19</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Irony: Group Project</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>আপনার গ্রুপের সদস্যরা প্রায় কোনো কাজ না করে শেষ মুহূর্তে ডেডলাইনের এক মিনিট আগে অ্যাসাইনমেন্ট জমা দিল।</t>
+          <t>Irony: Another Problem</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>সবাই দারুণ পরিশ্রম করেছে।</t>
+          <t>আপনি অনেক কষ্টে একটি কঠিন কাজ শেষ করলেন, কিন্তু সঙ্গে সঙ্গেই আরেকটি বড় সমস্যা তৈরি হলো।</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>কাজ না করার জন্য ব্যঙ্গ।</t>
+          <t>খারাপ গ্রুপ কাজ নিয়ে বিদ্রূপ।</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>সমস্যার ধারাবাহিকতা নিয়ে বিদ্রূপ।</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N20" t="n">
+        <v>14.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>33a29a1d-2ef2-4d5c-b116-0d5835cfb79f</t>
+          <t>112ce271-7baa-426d-ade1-dd4f86a917a7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-19T00:29:05</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:20:21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>20</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Irony: Another Problem</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>21</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>আপনি অনেক কষ্টে একটি কঠিন কাজ শেষ করলেন, কিন্তু সঙ্গে সঙ্গেই আরেকটি বড় সমস্যা তৈরি হলো।</t>
+          <t>Rhetorical Question: Repeated Mistake</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>কাজ শেষ করলাম, আরেকটা সমস্যা হাজির।</t>
+          <t>আপনার বন্ধু একই ভুল বারবার করছে, যদিও আপনি তাকে বিষয়টি অনেকবার বুঝিয়েছেন।</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>দুর্ভাগ্য প্রকাশ।</t>
+          <t>তুমি কতবার একই ভুল করবে?</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>বিরক্তি প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
         </is>
+      </c>
+      <c r="N21" t="n">
+        <v>29.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6f2c0673-830f-4c96-b74d-1790ac3be687</t>
+          <t>303e2fe5-b625-4150-be35-4bcfd7421b53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-19T00:29:49</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:21:01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>21</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Rhetorical Question: Repeated Mistake</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু একই ভুল বারবার করছে, যদিও আপনি তাকে বিষয়টি অনেকবার বুঝিয়েছেন।</t>
+          <t>Rhetorical Question: Exam</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>তুমি কতবার একই ভুল করবে?</t>
+          <t>একজন ব্যক্তি পরীক্ষার আগের দিন পড়াশোনা না করে অভিযোগ করছে যে তাকে কেন পড়তে হবে।</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>বিরক্তি প্রকাশ।</t>
+          <t>পরীক্ষার আগে পড়াশোনা না করলে কীভাবে হবে?</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>অভিযোগ (Complaint)</t>
         </is>
+      </c>
+      <c r="N22" t="n">
+        <v>39.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5b05374b-42fb-42c6-ac42-d1f1a97be98e</t>
+          <t>2feb82d4-032b-4023-b19f-1870448a0f08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-19T00:30:24</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:21:15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Rhetorical Question: Exam</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>23</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>একজন ব্যক্তি পরীক্ষার আগের দিন পড়াশোনা না করে অভিযোগ করছে যে তাকে কেন পড়তে হবে।</t>
+          <t>Rhetorical Question: Broken Object</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>পরীক্ষার আগে পড়তে হবে না?</t>
+          <t>আপনার ভাই/বোন কিছু ভেঙে ফেলেছে এবং এখন এমন আচরণ করছে যেন সে কিছুই জানে না।</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>পড়াশোনার প্রয়োজনীয়তা বোঝানো।</t>
+          <t>এটা কে ভাঙল, ভূত নাকি?</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>দোষারোপ।</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>14.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7d105c1c-b898-4dbc-9f4f-062b9811cfbe</t>
+          <t>1e159772-7af6-4bc6-a155-80900d76eb98</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-19T00:31:32</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:21:30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>23</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Rhetorical Question: Broken Object</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>24</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>আপনার ভাই/বোন কিছু ভেঙে ফেলেছে এবং এখন এমন আচরণ করছে যেন সে কিছুই জানে না।</t>
+          <t>Rhetorical Question: Tiredness</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>এটা কে ভাঙল?</t>
+          <t>আপনি সারাদিন কাজ করার পর ক্লান্ত, কিন্তু আপনার বন্ধু বারবার জিজ্ঞেস করছে কেন আপনি ক্লান্ত।</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>দায় এড়ানোর প্রতি প্রশ্ন।</t>
+          <t>সারাদিন কাজ করলে ক্লান্ত হব না নাকি?</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>ক্লান্তি জোর দিয়ে বলা।</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>15.45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ad69be24-10fa-4261-801a-2a467790de71</t>
+          <t>467d8749-e207-4ef5-8183-9072279ecb9d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-19T00:32:09</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:21:54</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>24</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Rhetorical Question: Tiredness</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>25</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>আপনি সারাদিন কাজ করার পর ক্লান্ত, কিন্তু আপনার বন্ধু বারবার জিজ্ঞেস করছে কেন আপনি ক্লান্ত।</t>
+          <t>Rhetorical Question: Ignored Advice</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>সারাদিন কাজ করলে ক্লান্ত হব না?</t>
+          <t>আপনি কাউকে বারবার সতর্ক করেছিলেন, সে আপনার কথা শোনেনি এবং এখন ঠিক সেই সমস্যায় পড়েছে।</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ক্লান্তি বোঝানো।</t>
+          <t>আমি কি বলিনি এটা হবে?</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>অন্যান্য (Other)</t>
-        </is>
+          <t>সতর্কতা না মানায় বিরক্তি।</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ব্যঙ্গ/ঠাট্টা (Sarcasm/Irony)</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>23.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dc866343-e1b4-4cf7-b556-faee03936193</t>
+          <t>0962de62-350f-44a2-988e-d952907333a9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-19T00:33:08</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:22:08</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>25</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Rhetorical Question: Ignored Advice</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>26</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>আপনি কাউকে বারবার সতর্ক করেছিলেন, সে আপনার কথা শোনেনি এবং এখন ঠিক সেই সমস্যায় পড়েছে।</t>
+          <t>Genuine Praise: Project</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>আমি কি বলিনি এটা হবে?</t>
+          <t>আপনার বন্ধু একটি কঠিন প্রজেক্ট সফলভাবে সম্পন্ন করেছে।</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>সতর্কতা উপেক্ষার প্রতি প্রশ্ন।</t>
+          <t>তুমি অসাধারণ কাজ করেছো</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>অন্যান্য (Other)</t>
-        </is>
+          <t>প্রশংসা।</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>14.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>55e1485f-2311-44f8-9c59-59a3f8f7ecb8</t>
+          <t>476524e3-a804-4db4-9658-0eaf08215fcc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-19T00:33:40</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:22:24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>26</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Genuine Praise: Project</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>27</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু একটি কঠিন প্রজেক্ট সফলভাবে সম্পন্ন করেছে।</t>
+          <t>Genuine Praise: Academic Result</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>তুমি অসাধারণ কাজ করেছো।</t>
+          <t>আপনার ছোট ভাই/বোন পরীক্ষায় খুব ভালো ফল করেছে।</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>সত্যিকারের প্রশংসা।</t>
+          <t>তোমার ফলাফল দেখে গর্ব হচ্ছে।</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>অভিনন্দন।</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
         </is>
+      </c>
+      <c r="N27" t="n">
+        <v>15.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2dbb2225-f606-4ebf-979d-cc7acfa5ae75</t>
+          <t>cfe62a9f-a1f5-4c6c-8a20-25cc50a612c9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-19T00:34:18</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:22:38</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>27</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Genuine Praise: Academic Result</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>28</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>আপনার ছোট ভাই/বোন পরীক্ষায় খুব ভালো ফল করেছে।</t>
+          <t>Appreciation: Help</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>তুমি দারুণ ফল করেছো।</t>
+          <t>একজন সহকর্মী আপনাকে একটি গুরুত্বপূর্ণ কাজ শেষ করতে সাহায্য করেছে।</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>সাফল্যের প্রশংসা।</t>
+          <t>তোমার সাহায্যের জন্য ধন্যবাদ।</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>কৃতজ্ঞতা।</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
         </is>
+      </c>
+      <c r="N28" t="n">
+        <v>14.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cabb0e49-a453-45d5-9739-846aa5f8350a</t>
+          <t>e7fb016e-ed6d-4c9a-b511-362fa1395333</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-19T00:34:47</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:22:53</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>28</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Appreciation: Help</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>29</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>একজন সহকর্মী আপনাকে একটি গুরুত্বপূর্ণ কাজ শেষ করতে সাহায্য করেছে।</t>
+          <t>Praise: Appearance</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>তুমি সাহায্য করায় অনেক ধন্যবাদ।</t>
+          <t>আপনার বন্ধু নতুন একটি পোশাক পরেছে এবং তাকে খুব সুন্দর দেখাচ্ছে।</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>কৃতজ্ঞতা প্রকাশ।</t>
+          <t>তোমাকে নতুন পোশাকে খুব সুন্দর লাগছে।</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>সৌন্দর্যের প্রশংসা।</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
         </is>
+      </c>
+      <c r="N29" t="n">
+        <v>14.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>144a1e00-8114-42a6-9b70-483e83b4a112</t>
+          <t>7df12fd2-b5ea-44ca-ab3a-23d3865581d2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-19T00:35:48</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:23:07</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>29</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Praise: Appearance</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>30</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু নতুন একটি পোশাক পরেছে এবং তাকে খুব সুন্দর দেখাচ্ছে।</t>
+          <t>Praise: Presentation</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>“তোমাকে নতুন পোশাকে খুব সুন্দর লাগছে।</t>
+          <t>আপনি আপনার বন্ধুর একটি খুব ভালো প্রেজেন্টেশন শুনলেন।</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>সৌন্দর্যের প্রশংসা।</t>
+          <t>তোমার প্রেজেন্টেশনটা দারুণ ছিল।</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>প্রশংসা।</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
         </is>
+      </c>
+      <c r="N30" t="n">
+        <v>14.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a5dcfe93-25f1-46d8-ae49-2a808c462405</t>
+          <t>7bfb33c7-841b-40fd-89ab-56238ae89dfb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-19T00:36:12</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:23:29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Praise: Presentation</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>31</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>আপনি আপনার বন্ধুর একটি খুব ভালো প্রেজেন্টেশন শুনলেন।</t>
+          <t>Complaint: Noise</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>তোমার প্রেজেন্টেশনটা দারুণ হয়েছে।</t>
+          <t>আপনার প্রতিবেশী সপ্তাহে কয়েকবার গভীর রাত পর্যন্ত জোরে গান বাজায়।</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>দক্ষতার প্রশংসা।</t>
+          <t>প্রতিদিন এত রাতে গান বাজালে বিরক্ত লাগে।</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
-        </is>
+          <t>প্রতিবেশীর শব্দ নিয়ে অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>অভিযোগ (Complaint)</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>21.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>47d0107d-60da-4145-b479-3eb2ac6dcf1e</t>
+          <t>a4f74f37-49d0-498e-b866-cd2d648b3dcd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-19T00:36:42</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:23:47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>31</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Complaint: Noise</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>32</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>আপনার প্রতিবেশী সপ্তাহে কয়েকবার গভীর রাত পর্যন্ত জোরে গান বাজায়।</t>
+          <t>Complaint: Late Delivery</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>রাতে এত জোরে গান বাজালে সমস্যা হয়।</t>
+          <t>আপনি অনলাইনে কিছু অর্ডার করেছিলেন, কিন্তু প্রতিশ্রুত সময়ের কয়েক দিন পরে সেটি এসেছে।</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>প্রতিবেশীর প্রতি অভিযোগ।</t>
+          <t>অর্ডারটা এত দেরিতে কেন এলো?</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>ডেলিভারি নিয়ে অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>অভিযোগ (Complaint)</t>
         </is>
+      </c>
+      <c r="N32" t="n">
+        <v>17.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>e7ba87b0-207c-4a41-894d-52243f1c8c95</t>
+          <t>c7ae199a-97c4-4df2-b89d-8d3728dc111e</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-19T00:37:02</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:24:02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>32</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Complaint: Late Delivery</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>33</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>আপনি অনলাইনে কিছু অর্ডার করেছিলেন, কিন্তু প্রতিশ্রুত সময়ের কয়েক দিন পরে সেটি এসেছে।</t>
+          <t>Complaint: Group Member</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>অর্ডারটা সময়মতো আসেনি।</t>
+          <t>আপনার গ্রুপের একজন সদস্য বারবার তার দায়িত্বের কাজ শেষ করছে না।</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ডেলিভারি বিলম্বের অভিযোগ।</t>
+          <t>তুমি বারবার কাজ শেষ করছো না।</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>দায়িত্বহীনতা নিয়ে অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>অভিযোগ (Complaint)</t>
         </is>
+      </c>
+      <c r="N33" t="n">
+        <v>14.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>741f2d81-af5c-47ab-9125-3f505c22561b</t>
+          <t>c28664f4-c4ab-49a6-9e6f-2fe74d80be4f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-19T00:37:28</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:24:19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>33</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Complaint: Group Member</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>34</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>আপনার গ্রুপের একজন সদস্য বারবার তার দায়িত্বের কাজ শেষ করছে না।</t>
+          <t>Complaint: Restaurant</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>তুমি বারবার কাজ শেষ করছো না।</t>
+          <t>আপনি রেস্টুরেন্টে খাবার অর্ডার করেছেন, কিন্তু খাবারটি আপনার প্রত্যাশার তুলনায় খুব খারাপ।</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>দায়িত্বহীনতার অভিযোগ।</t>
+          <t>খাবারটা একদমই ভালো না।</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>খাবার নিয়ে অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>অভিযোগ (Complaint)</t>
         </is>
+      </c>
+      <c r="N34" t="n">
+        <v>17.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08b3fc92-452d-4233-9e39-31d0fb722d88</t>
+          <t>f64efb4f-ea74-4e7a-8a26-c28fe7c81a53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-19T00:37:56</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:24:35</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>34</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Complaint: Restaurant</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>35</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>আপনি রেস্টুরেন্টে খাবার অর্ডার করেছেন, কিন্তু খাবারটি আপনার প্রত্যাশার তুলনায় খুব খারাপ।</t>
+          <t>Complaint: Cancelled Plans</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>খাবারটা প্রত্যাশার মতো হয়নি।</t>
+          <t>আপনার বন্ধু বারবার শেষ মুহূর্তে আপনাদের পরিকল্পনা বাতিল করছে।</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>খাবারের মান নিয়ে অভিযোগ।</t>
+          <t>তুমি সবসময় শেষ মুহূর্তে প্ল্যান বাতিল করো।</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>বন্ধুর আচরণ নিয়ে অভিযোগ।</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>অভিযোগ (Complaint)</t>
         </is>
+      </c>
+      <c r="N35" t="n">
+        <v>15.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13a26a9b-06f7-4d3f-8178-70547cf7e2c0</t>
+          <t>65cc1771-f211-4d03-a3f3-c689dc7884e7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-19T00:44:09</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:25:02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>35</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Complaint: Cancelled Plans</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>36</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু বারবার শেষ মুহূর্তে আপনাদের পরিকল্পনা বাতিল করছে।</t>
+          <t>Ambiguous: Good News</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>তুমি বারবার পরিকল্পনা বাতিল করছো।</t>
+          <t>আপনার বন্ধু সবেমাত্র একটি খুব ভালো খবর পেয়েছে।</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>বিরক্তি প্রকাশ।</t>
+          <t>ওহ, দারুণ খবর!</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>আনন্দ প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>27.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14d21e51-0444-4ee1-b55f-6001de3a3a2e</t>
+          <t>bf266e64-c3d0-4edf-a1c6-09f735d9601c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-19T00:44:31</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:25:23</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>36</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Ambiguous: Good News</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>37</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু সবেমাত্র একটি খুব ভালো খবর পেয়েছে।</t>
+          <t>Ambiguous: Serious Mistake</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>দারুণ খবর!</t>
+          <t>আপনার বন্ধু সবেমাত্র একটি গুরুতর ভুল করেছে।</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>আনন্দ প্রকাশ।</t>
+          <t>এটা তো বড় ভুল হলো।</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>প্রশংসা/ধন্যবাদ (Praise/Appreciation)</t>
-        </is>
+          <t>উদ্বেগ প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>অন্যান্য (Other)</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>20.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fb2d01ab-0858-43f6-82bf-d882ad2d25f6</t>
+          <t>56bfff2f-c22f-40b8-a0f3-45ab036efea1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-19T00:45:06</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:25:41</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>37</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Ambiguous: Serious Mistake</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>38</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু সবেমাত্র একটি গুরুতর ভুল করেছে।</t>
+          <t>Ambiguous: Uncertain Help</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>এটা খুব খারাপ হলো।</t>
+          <t>কেউ আপনাকে সাহায্য করবে বলেছে, কিন্তু সে সত্যিই সাহায্য করবে কি না তা নিয়ে আপনি নিশ্চিত নন।</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ভুলের গুরুত্ব বোঝানো।</t>
+          <t>তুমি সত্যিই সাহায্য করবে তো?</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>সন্দেহ প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>অন্যান্য (Other)</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>17.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2bb35e87-5850-47fa-9e0c-ce1c8fc34305</t>
+          <t>e98d0548-0283-42e7-b942-5a52d631ed3a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-19T00:45:36</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:26:02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>38</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Ambiguous: Uncertain Help</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>39</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>কেউ আপনাকে সাহায্য করবে বলেছে, কিন্তু সে সত্যিই সাহায্য করবে কি না তা নিয়ে আপনি নিশ্চিত নন।</t>
+          <t>Ambiguous: Waiting</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>তুমি সত্যিই সাহায্য করবে তো?</t>
+          <t>আপনি এমন একজনের জন্য অপেক্ষা করছেন যে ইতিমধ্যে ৩০ মিনিট দেরি করেছে এবং সে এখন এসে পৌঁছেছে।</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>সন্দেহ প্রকাশ।</t>
+          <t>অবশেষে এলেন!</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>মিশ্র প্রতিক্রিয়া।</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>অন্যান্য (Other)</t>
         </is>
+      </c>
+      <c r="N39" t="n">
+        <v>21.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06b1d239-db87-4989-ae94-2830b6ad7f88</t>
+          <t>87d54118-5a8c-41de-960c-5aaa78f9a0cb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-19T00:46:13</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:26:28</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>39</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Ambiguous: Waiting</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>40</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>আপনি এমন একজনের জন্য অপেক্ষা করছেন যে ইতিমধ্যে ৩০ মিনিট দেরি করেছে এবং সে এখন এসে পৌঁছেছে।</t>
+          <t>Ambiguous: Indirect No</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>অবশেষে তুমি এলে।</t>
+          <t>কেউ আপনাকে এমন কিছু করতে বলেছে যা আপনি করতে চান না, কিন্তু আপনি সরাসরি “না” বলতে চান না।</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>অপেক্ষার হতাশা/স্বস্তি।</t>
+          <t>আসলে আজকে একটু কঠিন হবে।</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>পরোক্ষভাবে না বলা।</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>অন্যান্য (Other)</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>26.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e60b1272-1425-4cbb-9d88-54e1c6141ce4</t>
+          <t>1e284783-4eed-46df-a99d-184d7872dc51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-19T00:46:46</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:27:03</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>40</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Ambiguous: Indirect No</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>41</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>কেউ আপনাকে এমন কিছু করতে বলেছে যা আপনি করতে চান না, কিন্তু আপনি সরাসরি “না” বলতে চান না।</t>
+          <t>Doubt</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>আজকে একটু ব্যস্ত আছি।</t>
+          <t>আপনার বন্ধু বলছে সে মাত্র ৩০ মিনিটে একটি অনেক বড় অ্যাসাইনমেন্ট শেষ করেছে।</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>সরাসরি না বলে অস্বীকৃতি।</t>
+          <t>৩০ মিনিটে এত বড় কাজ শেষ?</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>বন্ধুর দাবিতে অবিশ্বাস প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>অন্যান্য (Other)</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>35.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12a46fcb-1bdf-4da6-b4f7-5f4616718fa5</t>
+          <t>67a9c110-e510-4837-8b1a-e0c1909229a2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-19T00:47:15</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:27:24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>41</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Doubt</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>42</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু বলছে সে মাত্র ৩০ মিনিটে একটি অনেক বড় অ্যাসাইনমেন্ট শেষ করেছে।</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>৩০ মিনিটে এত বড় কাজ শেষ?</t>
+          <t>বহু বছর পর আপনি হঠাৎ একজন পুরোনো বন্ধুর সঙ্গে দেখা করলেন।</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>সন্দেহ প্রকাশ।</t>
+          <t>ওহ, এত বছর পর তোমাকে দেখছি!</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>পুরোনো বন্ধুকে দেখে আনন্দ প্রকাশ।</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>অন্যান্য (Other)</t>
         </is>
+      </c>
+      <c r="N42" t="n">
+        <v>21.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>681ca338-3d80-4c2b-bc1d-f0500196fe97</t>
+          <t>96c85ee4-cc4f-4052-84bc-3db229fb3a91</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-19T00:48:14</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:27:44</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>42</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>43</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>বহু বছর পর আপনি হঠাৎ একজন পুরোনো বন্ধুর সঙ্গে দেখা করলেন।</t>
+          <t>Disappointment</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ওহ, এতদিন পর তোমাকে দেখছি!</t>
+          <t>একটি গুরুত্বপূর্ণ অনুষ্ঠানে আপনি কারও সহযোগিতা আশা করেছিলেন, কিন্তু সে আসেনি।</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>আনন্দের বিস্ময়।</t>
+          <t>আমি ভেবেছিলাম তুমি আসবে।</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>অন্যান্য (Other)</t>
-        </is>
+          <t>সহযোগিতা না পাওয়ায় হতাশা।</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>অভিযোগ (Complaint)</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>19.22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e9d3d766-86c1-4e29-abe7-6c299aca4a56</t>
+          <t>a73bdc69-cdb6-4237-9f3a-28d458d49677</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-19T00:48:57</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:28:05</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>43</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Disappointment</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>44</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>একটি গুরুত্বপূর্ণ অনুষ্ঠানে আপনি কারও সহযোগিতা আশা করেছিলেন, কিন্তু সে আসেনি।</t>
+          <t>Sympathy</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>আমি তোমার সাহায্য আশা করেছিলাম।</t>
+          <t>আপনার বন্ধু জানাল যে সে একটি গুরুত্বপূর্ণ পরীক্ষায় ফেল করেছে।</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>হতাশা প্রকাশ।</t>
+          <t>দুঃখিত, তোমার জন্য খারাপ লাগছে।</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>বন্ধুর ব্যর্থতায় সহানুভূতি।</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>অন্যান্য (Other)</t>
         </is>
+      </c>
+      <c r="N44" t="n">
+        <v>21.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f86790a5-c15a-40a8-9440-caf30fa0a3fb</t>
+          <t>ff2ceba5-af59-4729-a3e6-176c206a3d6b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-19T00:49:51</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:28:21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>44</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sympathy</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>45</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>আপনার বন্ধু জানাল যে সে একটি গুরুত্বপূর্ণ পরীক্ষায় ফেল করেছে।</t>
+          <t>Frustration</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>দুঃখিত, তুমি ফেল করেছো।</t>
+          <t>আপনি একই সমস্যা কয়েকবার বুঝিয়েছেন, কিন্তু অন্য ব্যক্তি এখনও বিষয়টি বুঝতে পারছে না।</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>সহানুভূতি প্রকাশ।</t>
+          <t>কতবার বললাম, তবুও বুঝছো না।</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>অন্যান্য (Other)</t>
-        </is>
+          <t>বারবার না বোঝায় বিরক্তি।</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>অভিযোগ (Complaint)</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>16.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>c3bc796b-7e22-420b-b199-07488cffa7d8</t>
+          <t>410d6a58-4f43-445b-9738-bdba24d6c9fa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-19T00:50:20</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:28:46</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Frustration</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>46</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>আপনি একই সমস্যা কয়েকবার বুঝিয়েছেন, কিন্তু অন্য ব্যক্তি এখনও বিষয়টি বুঝতে পারছে না।</t>
+          <t>Teacher–Student</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>কতবার বলব একই কথা?</t>
+          <t>আপনি একটি অ্যাসাইনমেন্ট দেরিতে জমা দিয়েছেন এবং শিক্ষক জিজ্ঞেস করলেন কেন দেরি হয়েছে।</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>বিরক্তি প্রকাশ।</t>
+          <t>স্যার, কিছু সমস্যার কারণে দেরি হয়েছে।</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
+          <t>শিক্ষকের কাছে দেরির কারণ ভদ্রভাবে বলা।</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>অন্যান্য (Other)</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>25.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>017b6913-a7e5-449d-a513-b4d7ec4e0ed8</t>
+          <t>eebf8531-9888-4884-8cd4-2d8d4667aeca</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-19T00:50:59</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:29:14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>46</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Teacher–Student</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>47</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>আপনি একটি অ্যাসাইনমেন্ট দেরিতে জমা দিয়েছেন এবং শিক্ষক জিজ্ঞেস করলেন কেন দেরি হয়েছে।</t>
+          <t>Workplace</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>দুঃখিত, সময়মতো জমা দিতে পারিনি।”</t>
+          <t>আপনার সুপারভাইজার আপনাকে আরও একটি কাজ দিলেন, অথচ আপনার হাতে ইতিমধ্যে কয়েকটি জরুরি কাজ আছে।</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>দেরির কারণ ব্যাখ্যা।</t>
+          <t>আমার হাতে ইতিমধ্যে অনেক কাজ আছে।</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>সুপারভাইজারকে কাজের চাপ বোঝানো।</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
           <t>অন্যান্য (Other)</t>
         </is>
+      </c>
+      <c r="N47" t="n">
+        <v>27.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>f7317124-5f98-43e1-86b0-652b55f4be8d</t>
+          <t>266d274d-dc78-40b2-a103-36a0d68a6f67</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-19T00:52:04</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:29:38</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>47</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Workplace</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>48</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>আপনার সুপারভাইজার আপনাকে আরও একটি কাজ দিলেন, অথচ আপনার হাতে ইতিমধ্যে কয়েকটি জরুরি কাজ আছে।</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>আমার হাতে ইতিমধ্যে অনেক কাজ আছে।</t>
+          <t>আপনার পরিবার আপনাকে একটি অনুষ্ঠানে যেতে বলছে, কিন্তু আপনার গুরুত্বপূর্ণ একাডেমিক কাজ আছে।</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>অতিরিক্ত কাজের চাপ বোঝানো।</t>
+          <t>আপনি ধাক্কা দিলেন, ক্ষমা চাইতে পারতেন।</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>অস্বীকৃতি/না বলা (Refusal)</t>
-        </is>
+          <t>অপরিচিতকে অভিযোগ করা।</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>অভিযোগ (Complaint)</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>23.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5523b3a0-27f0-4624-be24-103a8ac04a03</t>
+          <t>f54d4a0b-65f1-4102-b490-15f071459909</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-19T00:52:46</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:30:11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>48</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>49</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>আপনার পরিবার আপনাকে একটি অনুষ্ঠানে যেতে বলছে, কিন্তু আপনার গুরুত্বপূর্ণ একাডেমিক কাজ আছে।</t>
+          <t>Stranger</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>আজকে আমার পড়াশোনার কাজ আছে।</t>
+          <t>ভিড়ের মধ্যে একজন অপরিচিত ব্যক্তি আপনাকে ধাক্কা দিলেন এবং ক্ষমা চাইলেন না।</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>অনুষ্ঠানে না যাওয়ার কারণ।</t>
+          <t>আমি কিছু জানি না।</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>বন্ধুর গোপনীয়তা রক্ষা করা।</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
         </is>
+      </c>
+      <c r="N49" t="n">
+        <v>32.76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6ee69c13-ac39-466d-b68c-4d727a2779bd</t>
+          <t>a011c815-ceb6-45d3-b901-1b440a627735</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-19T00:53:33</t>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>2026-09-01T22:30:55</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>25–34</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>49</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Stranger</t>
-        </is>
+          <t>Almost always</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Standard Bangla</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>50</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ভিড়ের মধ্যে একজন অপরিচিত ব্যক্তি আপনাকে ধাক্কা দিলেন এবং ক্ষমা চাইলেন না।</t>
+          <t>Keeping a Secret</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>আপনি ধাক্কা দিলেন, ক্ষমা চাইবেন না?</t>
+          <t>আপনার বন্ধু আপনাকে একটি ব্যক্তিগত বিষয় বলেছে এবং কাউকে না বলতে অনুরোধ করেছে। পরে অন্য একজন বন্ধু বিষয়টি সম্পর্কে জানতে চাইল।</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>অপরিচিত ব্যক্তির আচরণে অসন্তোষ প্রকাশ।</t>
+          <t>আমি কিছু জানি না।</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>অভিযোগ (Complaint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>e91e2b69-96e9-43a3-9e2d-4b33e3d1b8da</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-08-19T00:54:01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Under 18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Secondary</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Almost always</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Standard Bangla</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>50</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Keeping a Secret</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>আপনার বন্ধু আপনাকে একটি ব্যক্তিগত বিষয় বলেছে এবং কাউকে না বলতে অনুরোধ করেছে। পরে অন্য একজন বন্ধু বিষয়টি সম্পর্কে জানতে চাইল।</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>আমি এ বিষয়ে কিছু বলতে পারব না।</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>বন্ধুর ব্যক্তিগত বিষয় গোপন রাখা।</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
+          <t>বন্ধুর গোপনীয়তা রক্ষা করা।</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>অস্বীকৃতি/না বলা (Refusal)</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>44.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Participant_ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Completion_Time_Minutes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>U1_Instructions_Clear</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>U2_Scenarios_Understandable</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>U3_Interface_Easy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>U4_Example_Helpful</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>U5_Progress_Useful</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>U6_Easy_to_Express_Meaning</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>U7_Questionnaire_Length_Reasonable</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>U8_Comfortable_Using_System</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>U9_Willing_to_Reuse</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>U10_Overall_Satisfaction</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Open_Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9f50735f-42a4-440a-bce5-058dcf59880c</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
